--- a/microservice-common-export/unittest-excel-out.xlsx
+++ b/microservice-common-export/unittest-excel-out.xlsx
@@ -141,7 +141,7 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>46139.07417931713</v>
+        <v>46144.71102178241</v>
       </c>
     </row>
     <row r="3">
@@ -166,7 +166,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>46139.07417931713</v>
+        <v>46144.71102178241</v>
       </c>
     </row>
   </sheetData>
